--- a/results/andar_할인율모니터링_20261025.xlsx
+++ b/results/andar_할인율모니터링_20261025.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,7 +659,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>376</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>538</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>538</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>538</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10,223</t>
+          <t>10,224</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1373,39 +1373,39 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18772&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=19330&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EPTFR-01</t>
+          <t>EPTSC-12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>폼롤러</t>
+          <t>소프트 니트 기모 오버 니삭스</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1427,27 +1427,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18772&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17425&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EPTFR-02</t>
+          <t>EPTSC-06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>폼롤러</t>
+          <t>필라테스 크루 삭스</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1457,39 +1457,39 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17425&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EPTSC-06</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>필라테스 크루 삭스</t>
+          <t>레그 미들 워머</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1499,54 +1499,54 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>레그 미들 워머</t>
+          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>15,800</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>3,266</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1595,37 +1595,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16032&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>EOTCP-05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
+          <t>히트 런 이어플랩 캡</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>15,800</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3,266</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1679,27 +1679,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16032&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18773&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EOTCP-05</t>
+          <t>EPTBG-11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>히트 런 이어플랩 캡</t>
+          <t>안다르 실버 리유저블백 L</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1721,27 +1721,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16649&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18854&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EPTBG-02</t>
+          <t>EPTBG-10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>서밋 유틸리티 백팩</t>
+          <t>미니 크레센트 듀얼백</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>89,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>89,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1751,39 +1751,39 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18854&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16649&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EPTBG-10</t>
+          <t>EPTBG-02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>미니 크레센트 듀얼백</t>
+          <t>서밋 유틸리티 백팩</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>89,000</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>89,000</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1793,39 +1793,39 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>176</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18773&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EPTBG-11</t>
+          <t>ENTSO-02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>안다르 실버 리유저블백 L</t>
+          <t>안다르 제트플라이 (우먼즈)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1,074</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ENTSO-02</t>
+          <t>ENTSO-12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1889,27 +1889,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ENTSO-12</t>
+          <t>EOTBG-03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (우먼즈)</t>
+          <t>데이 앤 트래블 숄더백</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1,074</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -1973,27 +1973,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EOTBG-03</t>
+          <t>ENTSC-24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>데이 앤 트래블 숄더백</t>
+          <t>웜 슬릿 레그 워머</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>304</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
@@ -2057,27 +2057,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13838&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ENTSC-24</t>
+          <t>EOTFB-01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>웜 슬릿 레그 워머</t>
+          <t>에어쿨링 와이드 헤드밴드</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2087,39 +2087,39 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>2,560</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13838&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18769&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EOTFB-01</t>
+          <t>EPTBG-07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>에어쿨링 와이드 헤드밴드</t>
+          <t>멀티 포켓 파우치</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2129,39 +2129,39 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2,559</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=19339&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EPTCP-05</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>히트 런 이어플랩 캡 2.0</t>
+          <t>맨즈 논슬립 풀 토삭스</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2171,39 +2171,39 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18948&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15732&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EPTCP-04</t>
+          <t>EOTSC-11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>라이트 에어 러닝 캡</t>
+          <t>웜 레그 롱 워머</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2213,35 +2213,39 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18948&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>EPTCP-04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>맨즈 논슬립 풀 토삭스</t>
+          <t>라이트 에어 러닝 캡</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2251,14 +2255,10 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2,089</t>
+          <t>2,090</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2305,27 +2305,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15732&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17414&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EOTSC-11</t>
+          <t>EPTBG-01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>웜 레그 롱 워머</t>
+          <t>에어플라이 프리런 러닝 벨트</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2335,81 +2335,81 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18769&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EPTBG-07</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>멀티 포켓 파우치</t>
+          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>737</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17414&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=19339&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EPTBG-01</t>
+          <t>EPTCP-05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>에어플라이 프리런 러닝 벨트</t>
+          <t>히트 런 이어플랩 캡 2.0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2419,49 +2419,49 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EPTET-01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
+          <t>언더웨어 파우치</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>378</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2473,27 +2473,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18772&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EJFST-02</t>
+          <t>EPTFR-01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>릴렉스 요가링</t>
+          <t>폼롤러</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>6,676</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18772&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EPTET-01</t>
+          <t>EPTFR-02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>언더웨어 파우치</t>
+          <t>폼롤러</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2545,81 +2545,81 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12511&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EOTMK-01</t>
+          <t>ENTSO-03</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
+          <t>안다르 이지무브 화이트</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>129,000</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>64,500</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1,145</t>
+          <t>508</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>EJFST-02</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 니삭스</t>
+          <t>릴렉스 요가링</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2629,39 +2629,39 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>6,676</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14076&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EOTBG-13</t>
+          <t>EOTMK-01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>멀티 포켓 숄더 앤 크로스백</t>
+          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2671,29 +2671,29 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>1,145</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EPTSC-04</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>필라테스 토삭스</t>
+          <t>논슬립 퍼포먼스 니삭스</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>767</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2725,7 +2725,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12511&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12512&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>안다르 이지무브 화이트</t>
+          <t>안다르 이지무브 베이지</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>427</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
@@ -2809,27 +2809,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14076&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EPTBG-03</t>
+          <t>EOTBG-13</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>컴팩트 포켓 크로스백</t>
+          <t>멀티 포켓 숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>434</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2851,27 +2851,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EOTBG-20</t>
+          <t>EPTSC-04</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>클라우드 스트링 쇼퍼백</t>
+          <t>필라테스 토삭스</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2893,27 +2893,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16045&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EOTBG-21</t>
+          <t>EOTMU-01</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>데일리 라운드백</t>
+          <t>스트링 패딩 넥워머</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2923,54 +2923,54 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13604&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[2ea] 하이 서포트 무릎 보호대</t>
+          <t>[1&amp;1] 올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3019,27 +3019,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11458&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ENTSC-13</t>
+          <t>EOTBG-20</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 크루삭스</t>
+          <t>클라우드 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3049,91 +3049,91 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12512&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ENTSO-03</t>
+          <t>EOTBG-21</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>안다르 이지무브 베이지</t>
+          <t>데일리 라운드백</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>129,000</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>64,500</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16045&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13604&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EOTMU-01</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>스트링 패딩 넥워머</t>
+          <t>[2ea] 하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>756</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3187,27 +3187,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18767&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11458&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EPTBG-06</t>
+          <t>ENTSC-13</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>컴팩트 포켓 스퀘어 크로스백</t>
+          <t>논슬립 퍼포먼스 크루삭스</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3217,49 +3217,49 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>681</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18767&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>EPTBG-06</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[1&amp;1] 올데이 기모 삭스</t>
+          <t>컴팩트 포켓 스퀘어 크로스백</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3313,27 +3313,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16640&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EPTBG-05</t>
+          <t>ENTSC-20</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>안다르 시그니처 로고 에코백</t>
+          <t>시그니처 로고 크루 삭스</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3343,39 +3343,39 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>627</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16640&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EOTCP-01</t>
+          <t>EPTBG-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>올라운드 버킷햇</t>
+          <t>안다르 시그니처 로고 에코백</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3385,39 +3385,39 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ENTSC-20</t>
+          <t>EOTCP-01</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>시그니처 로고 크루 삭스</t>
+          <t>올라운드 버킷햇</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3427,54 +3427,54 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11962&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ENTMT-01</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>레스트 인 마블 요가매트 (4mm)</t>
+          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>556</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3523,69 +3523,69 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>ENTSO-12</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
+          <t>안다르 제트플라이 (맨즈)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>703</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11962&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EOTBG-12</t>
+          <t>ENTMT-01</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>프리런 벨크로 러닝 벨트</t>
+          <t>레스트 인 마블 요가매트 (4mm)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -3649,27 +3649,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EJFMB-03</t>
+          <t>EOTBG-12</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>릴렉스 짐볼 65cm</t>
+          <t>프리런 벨크로 러닝 벨트</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2,134</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3691,27 +3691,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18761&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EPTRB-02</t>
+          <t>EJFMB-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9스텝 스트레칭 밴드</t>
+          <t>릴렉스 짐볼 65cm</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3721,39 +3721,39 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2,134</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18765&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EPTSV-03</t>
+          <t>EPTSC-11</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
+          <t>데일리 쿠션 크루 삭스</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3763,39 +3763,39 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12318&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18761&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ENTBG-13</t>
+          <t>EPTRB-02</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>데일리 스퀘어백</t>
+          <t>9스텝 스트레칭 밴드</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3817,27 +3817,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18765&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12318&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EPTSC-11</t>
+          <t>ENTBG-13</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>데일리 쿠션 크루 삭스</t>
+          <t>데일리 스퀘어백</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>442</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3901,27 +3901,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>EPTSV-03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
+          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3943,27 +3943,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EKPMT-03</t>
+          <t>EOTGL-04</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>릴렉스 논슬립 요가 타월</t>
+          <t>논슬립 스킨 요기 글러브</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>35,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>35,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3973,39 +3973,39 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1,598</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EOTGL-04</t>
+          <t>EKPMT-03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>논슬립 스킨 요기 글러브</t>
+          <t>릴렉스 논슬립 요가 타월</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>35,900</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>35,900</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4015,12 +4015,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>1,598</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -4153,42 +4153,42 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>579</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4237,42 +4237,42 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>[1&amp;1] 램스울 크루 삭스</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -4363,27 +4363,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18759&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EPTMB-01</t>
+          <t>ENTSC-12</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>마사지 싱글볼</t>
+          <t>논슬립 퍼포먼스 토삭스</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4393,39 +4393,39 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4,146</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EOTBG-14</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>폴더블 캐리백 2.0</t>
+          <t>[1ea] 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4435,81 +4435,81 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>756</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>라이트 러닝 베스트</t>
+          <t>[1&amp;1] 램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>884</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ENTSC-12</t>
+          <t>EMTSC-01</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 토삭스</t>
+          <t>링글 크루 삭스</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4519,81 +4519,81 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>4,146</t>
+          <t>1,357</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18759&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>EPTMB-01</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
+          <t>마사지 싱글볼</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EMTSC-01</t>
+          <t>EOTBG-14</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>링글 크루 삭스</t>
+          <t>폴더블 캐리백 2.0</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4603,39 +4603,39 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1,357</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17424&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EPTSC-05</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>필라테스 앵클 삭스</t>
+          <t>라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4645,39 +4645,39 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17424&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EPTCP-03</t>
+          <t>EPTSC-05</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>썬가드 와이드 버킷햇</t>
+          <t>필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4687,81 +4687,81 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>논슬립 스킨 하프 토삭스</t>
+          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>398</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18760&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EPTMB-02</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>마사지 듀얼볼</t>
+          <t>논슬립 스킨 하프 토삭스</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4783,27 +4783,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16650&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EPTCP-02</t>
+          <t>EOTSC-06</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>시그니처 로고 나일론 볼캡</t>
+          <t>서포트 쿠션 러닝 삭스</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4813,39 +4813,39 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>793</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EPTCP-03</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
+          <t>썬가드 와이드 버킷햇</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4855,71 +4855,71 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>ENTFB-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>[2ea] 서포트 발목 보호대</t>
+          <t>에어쿨링 라인 스크런치</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>817</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EOTSC-06</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>서포트 쿠션 러닝 삭스</t>
+          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4939,39 +4939,39 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>654</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18760&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EPTMB-02</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>[1ea] 하이 서포트 무릎 보호대</t>
+          <t>마사지 듀얼볼</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4981,39 +4981,39 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16650&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EOTSC-13</t>
+          <t>EPTCP-02</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>테이핑 러닝 삭스</t>
+          <t>시그니처 로고 나일론 볼캡</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5035,27 +5035,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ENTFB-01</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>에어쿨링 라인 스크런치</t>
+          <t>[1ea] 하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5065,39 +5065,39 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>756</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EOTSV-03</t>
+          <t>EOTSC-13</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>[1ea] 서포트 허리 보호대</t>
+          <t>테이핑 러닝 삭스</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5107,39 +5107,39 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>313</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6662&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13842&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EKPMB-02</t>
+          <t>EOTBG-04</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>릴렉스 미니 짐볼</t>
+          <t>데님 포켓 숄더백</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5149,39 +5149,39 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>1,252</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6662&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EKPMB-01</t>
+          <t>EKPMB-02</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>릴렉스 웨이트볼 0.5kg</t>
+          <t>릴렉스 미니 짐볼</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5191,39 +5191,39 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>1,252</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=19330&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EPTSC-12</t>
+          <t>EPTBG-03</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>소프트 니트 기모 오버 니삭스</t>
+          <t>컴팩트 포켓 크로스백</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>170</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -5371,27 +5371,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EOTCP-06</t>
+          <t>ENTFB-05</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>소프트 니트 버킷햇</t>
+          <t>소프트 니트 헤드밴드</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>919</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5413,27 +5413,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ENTFB-05</t>
+          <t>EOTCP-06</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>소프트 니트 헤드밴드</t>
+          <t>소프트 니트 버킷햇</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5455,17 +5455,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
+          <t>[2ea] 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5475,91 +5475,91 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>756</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EPTSC-08</t>
+          <t>EOTSV-03</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
+          <t>[1ea] 서포트 허리 보호대</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ENTSO-12</t>
+          <t>EOTSC-12</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (맨즈)</t>
+          <t>소프트 니트 기모 니삭스</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5569,123 +5569,123 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EOTSC-12</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>소프트 니트 기모 니삭스</t>
+          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EMTSV-06</t>
+          <t>EPTSC-08</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>에어쿨링 손목 보호대</t>
+          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>1,121</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15143&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EOTBG-17</t>
+          <t>EMTSV-06</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>3 in 1 캐리온 더플백</t>
+          <t>에어쿨링 손목 보호대</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>109,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>109,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5695,39 +5695,39 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1,122</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15371&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15143&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EOTBG-15</t>
+          <t>EOTBG-17</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>폴더블 짐백 2.0</t>
+          <t>3 in 1 캐리온 더플백</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>109,000</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>109,000</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5749,27 +5749,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=19316&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EOTGL-03</t>
+          <t>EPTSC-10</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>소프트 니트 플립 글러브</t>
+          <t>니트 루즈 오버 니삭스</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5779,39 +5779,39 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>EOTGL-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>[1ea] 서포트 발목 보호대</t>
+          <t>소프트 니트 플립 글러브</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5833,27 +5833,27 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=19316&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15371&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EPTSC-10</t>
+          <t>EOTBG-15</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>니트 루즈 오버 니삭스</t>
+          <t>폴더블 짐백 2.0</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5863,165 +5863,165 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>EKPRB-04</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
+          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>41,800</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>35,600</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>473</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EPTSC-03</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>[1&amp;1] 데일리 루즈 삭스</t>
+          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>41,800</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>18,900</t>
+          <t>35,600</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>605</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EPTSC-03</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>논슬립 스킨 토삭스</t>
+          <t>[1&amp;1] 데일리 루즈 삭스</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>18,900</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EPTFB-02</t>
+          <t>EOTSC-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>퍼포먼스 심리스 손목밴드</t>
+          <t>시그니처 로고 맨즈 크루 삭스</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6043,27 +6043,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EKPRB-04</t>
+          <t>EPTFB-02</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
+          <t>퍼포먼스 심리스 손목밴드</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6073,39 +6073,39 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EOTSC-10</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>시그니처 로고 맨즈 크루 삭스</t>
+          <t>논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6115,81 +6115,81 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>[2ea] 서포트 팔꿈치 보호대</t>
+          <t>컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EKPMB-01</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>컴프레션 러닝 니삭스</t>
+          <t>릴렉스 웨이트볼 0.5kg</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6199,49 +6199,49 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>716</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>[1&amp;1] 3D 쿨링 팔토시</t>
+          <t>[2ea] 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>25,900</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>606</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6253,27 +6253,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12765&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>ENTBG-16</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>레그 숏 워머</t>
+          <t>라이트 패딩 쇼퍼백</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>635</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6295,27 +6295,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EMTBG-12</t>
+          <t>EOTSC-19</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>데일리 쇼퍼백</t>
+          <t>레그 숏 워머</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>1,438</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6379,42 +6379,42 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EPTET-03</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>안다르 3단 양우산</t>
+          <t>[1&amp;1] 3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>25,900</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>569</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -6463,27 +6463,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17387&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EOTSC-05</t>
+          <t>EPTSC-08</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>올데이 수피마 앵클 삭스</t>
+          <t>맨즈 필라테스 크루 삭스</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -6547,27 +6547,27 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15865&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EOTBG-11</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>메쉬 파우치</t>
+          <t>올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6577,39 +6577,39 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17387&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EPTSC-08</t>
+          <t>EOTBG-11</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>맨즈 필라테스 크루 삭스</t>
+          <t>메쉬 파우치</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2,089</t>
+          <t>2,090</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6673,27 +6673,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ENTBG-03</t>
+          <t>EOTCP-02</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>데일리 스트링 쇼퍼백</t>
+          <t>데님 로고 볼캡</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6703,39 +6703,39 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EOTCP-02</t>
+          <t>EOTSC-01</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>데님 로고 볼캡</t>
+          <t>프레시 필드 니삭스</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>311</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6757,27 +6757,27 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EOTSC-01</t>
+          <t>EMTBG-12</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>프레시 필드 니삭스</t>
+          <t>데일리 쇼퍼백</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>1,438</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6799,27 +6799,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EOTBG-10</t>
+          <t>EOTSC-05</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>에어플라이 투웨이 프리런 백 3.0</t>
+          <t>올데이 수피마 앵클 삭스</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6829,39 +6829,39 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>1,173</t>
+          <t>485</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11110&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>ENTCP-01</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>맨즈 필라테스 앵클 삭스</t>
+          <t>와이드 셰이드 버킷햇</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6871,39 +6871,39 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>689</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12765&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ENTBG-16</t>
+          <t>EPTET-03</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>라이트 패딩 쇼퍼백</t>
+          <t>안다르 3단 양우산</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6913,39 +6913,39 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.4</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15865&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>올데이 기모 삭스</t>
+          <t>맨즈 필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6955,39 +6955,39 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9599&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EOTSV-04</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>프리런 라이트 러닝 밴드</t>
+          <t>리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6997,39 +6997,39 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>398</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13842&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14561&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EOTBG-04</t>
+          <t>EOTBG-05</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>데님 포켓 숄더백</t>
+          <t>메쉬 포켓 비치백</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7039,39 +7039,39 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11110&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11963&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ENTCP-01</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>와이드 셰이드 버킷햇</t>
+          <t>맨즈 논슬립 하프 토삭스</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7093,27 +7093,27 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14561&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EOTBG-05</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>메쉬 포켓 비치백</t>
+          <t>릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7123,39 +7123,39 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>605</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EOTCP-03</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>쿨 라운드 볼캡</t>
+          <t>[1ea] 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7165,39 +7165,39 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>606</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16630&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EPTSV-02</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>하이 서포트 발목 보호대</t>
+          <t>램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7207,81 +7207,81 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>366</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9599&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>리브드 셔링 루즈 삭스</t>
+          <t>에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>574</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>EOTBG-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>릴렉스 소프트 웨이트바 1kg</t>
+          <t>에어플라이 투웨이 프리런 백 3.0</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7291,39 +7291,39 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>1,173</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>EOTSV-04</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>[1ea] 서포트 팔꿈치 보호대</t>
+          <t>프리런 라이트 러닝 밴드</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7333,39 +7333,39 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>131</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.2</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>램스울 크루 삭스</t>
+          <t>[1ea] 하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7375,49 +7375,49 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>164</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17842&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>EPTSC-03</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>에어컴피 크루 삭스</t>
+          <t>데일리 루즈 삭스</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7429,27 +7429,27 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11963&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17436&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>EPTSV-01</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>맨즈 논슬립 하프 토삭스</t>
+          <t>3D 쿨링 핑거홀 팔토시</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>184</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7471,27 +7471,27 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>[1ea] 하이 서포트 팔꿈치 보호대</t>
+          <t>맨즈 라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7501,39 +7501,39 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17842&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15151&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>EPTSC-03</t>
+          <t>EOTBG-22</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>데일리 루즈 삭스</t>
+          <t>투포켓 로고 캔버스백</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7543,39 +7543,39 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17436&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>EPTSV-01</t>
+          <t>EOTBO-01</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>3D 쿨링 핑거홀 팔토시</t>
+          <t>액티브 스포츠 보틀 (650ml)</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>358</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7597,27 +7597,27 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>EOTCP-03</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>맨즈 라이트 러닝 베스트</t>
+          <t>쿨 라운드 볼캡</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7627,39 +7627,39 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15151&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>EOTBG-22</t>
+          <t>ENTBG-14</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>투포켓 로고 캔버스백</t>
+          <t>웨이브 패딩 파우치</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7669,39 +7669,39 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12488&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>EOTBO-01</t>
+          <t>ENTBG-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>액티브 스포츠 보틀 (650ml)</t>
+          <t>스퀘어 크로스백</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7711,39 +7711,39 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>646</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12096&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ENTBG-14</t>
+          <t>ENTET-02</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>웨이브 패딩 파우치</t>
+          <t>릴렉스 소프트 웨이트바 2kg</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -7753,39 +7753,39 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12488&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11208&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ENTBG-10</t>
+          <t>ENTSC-21</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>스퀘어 크로스백</t>
+          <t>링글 오버 니삭스</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>321</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -7807,69 +7807,69 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12096&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11092&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ENTET-02</t>
+          <t>ENTSC-05</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>릴렉스 소프트 웨이트바 2kg</t>
+          <t>에어프레시 크루 삭스</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>575</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11208&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ENTSC-21</t>
+          <t>ENTBG-03</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>링글 오버 니삭스</t>
+          <t>데일리 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7879,94 +7879,52 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>754</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11092&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9023&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ENTSC-05</t>
+          <t>EMTBG-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>에어프레시 크루 삭스</t>
+          <t>숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>8,370</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9023&amp;cate_no=2100&amp;display_group=1</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>EMTBG-03</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>숄더 앤 크로스백</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>59,000</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>59,000</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>8,370</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
